--- a/reports/二级子公司D_现金流量表_2026-09.xlsx
+++ b/reports/二级子公司D_现金流量表_2026-09.xlsx
@@ -1957,16 +1957,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F3" s="28" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
-      <c r="G3" s="28" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
+      <c r="F3" s="28" t="n"/>
+      <c r="G3" s="28" t="n"/>
       <c r="I3" s="5" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -1996,10 +1988,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>75921300</v>
+        <v>73566240</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>628917588</v>
+        <v>610803211</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2030,10 +2022,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>1511959</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>13073305</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2063,10 +2055,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>750212</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>6535725</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2096,10 +2088,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>378588</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>3270536</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2129,10 +2121,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>299898</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>2612745</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2162,10 +2154,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>227060</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>1963192</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2195,10 +2187,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>150160</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>1306045</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2228,10 +2220,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>113277</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>981626</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2261,10 +2253,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>75294</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>653149</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2294,10 +2286,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>188199</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>1635395</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2327,10 +2319,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>94898</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>821081</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2360,10 +2352,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>59671</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>519628</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2393,10 +2385,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>194670</v>
+        <v>189865</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>1688994</v>
+        <v>1640387</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2426,10 +2418,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>1297800</v>
+        <v>1253725</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>11259960</v>
+        <v>10924711</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2546,7 +2538,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>77413770</v>
+        <v>78859046</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2577,10 +2569,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>49749000</v>
+        <v>48308807</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>431631800</v>
+        <v>419405030</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2610,10 +2602,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>503034</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>4355812</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2643,10 +2635,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>375656</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>3269405</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2676,10 +2668,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>252173</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>2179388</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2709,10 +2701,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>187473</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>1633577</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2742,10 +2734,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>126208</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>1090378</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2775,10 +2767,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>94222</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>820566</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2808,10 +2800,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>7786800</v>
+        <v>7589718</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>67559760</v>
+        <v>65662510</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2841,10 +2833,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>4109700</v>
+        <v>3979070</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>35656540</v>
+        <v>34580871</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2874,10 +2866,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>1622250</v>
+        <v>1576987</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>14074950</v>
+        <v>13678092</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2936,7 +2928,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>63267750</v>
+        <v>62993348</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2967,7 +2959,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>14146020</v>
+        <v>15865698</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -3093,10 +3085,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>82400</v>
+        <v>80361</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>741600</v>
+        <v>720764</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3159,10 +3151,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>721000</v>
+        <v>701597</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>6489000</v>
+        <v>6306779</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3192,10 +3184,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>432600</v>
+        <v>419689</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>3893400</v>
+        <v>3776556</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3225,7 +3217,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>803400</v>
+        <v>781958</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3256,10 +3248,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>8240000</v>
+        <v>8019201</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>74160000</v>
+        <v>71976730</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3289,10 +3281,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>1236000</v>
+        <v>1195591</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>11124000</v>
+        <v>10799582</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3322,10 +3314,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>5665000</v>
+        <v>5525104</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>50985000</v>
+        <v>49519629</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3454,10 +3446,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>185400</v>
+        <v>180574</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>1668600</v>
+        <v>1621820</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3487,7 +3479,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>8425400</v>
+        <v>8199775</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3518,7 +3510,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-7622000</v>
+        <v>-7417817</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3578,10 +3570,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>1545000</v>
+        <v>1495723</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>13905000</v>
+        <v>13502792</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3644,10 +3636,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>2575000</v>
+        <v>2488113</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>23175000</v>
+        <v>22488609</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3677,10 +3669,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>2575000</v>
+        <v>2512499</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>23175000</v>
+        <v>22518037</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3710,10 +3702,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>82400</v>
+        <v>79622</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>741600</v>
+        <v>719271</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3743,7 +3735,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>4202400</v>
+        <v>4063458</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3774,10 +3766,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>2060000</v>
+        <v>1994469</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>18540000</v>
+        <v>17980066</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3807,10 +3799,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>2060000</v>
+        <v>2002583</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>18540000</v>
+        <v>18017643</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3840,10 +3832,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>329600</v>
+        <v>320102</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>2966400</v>
+        <v>2877837</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3902,10 +3894,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>288400</v>
+        <v>280916</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>2595600</v>
+        <v>2519778</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3935,10 +3927,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>41200</v>
+        <v>39828</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>370800</v>
+        <v>359901</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3968,7 +3960,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>2430800</v>
+        <v>2354399</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3999,7 +3991,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>1771600</v>
+        <v>1709059</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -4059,7 +4051,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>8295620</v>
+        <v>10156940</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -4090,7 +4082,9 @@
         </is>
       </c>
       <c r="F69" s="23" t="n"/>
-      <c r="G69" s="20" t="n"/>
+      <c r="G69" s="20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="9" t="inlineStr">
@@ -4119,7 +4113,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>8295620</v>
+        <v>10156940</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
